--- a/data/demo_batch_learners_with_errors.xlsx
+++ b/data/demo_batch_learners_with_errors.xlsx
@@ -587,7 +587,7 @@
         <v>39</v>
       </c>
       <c r="G6">
-        <v>0.461538461538462</v>
+        <v>0.46</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -657,7 +657,7 @@
         <v>48</v>
       </c>
       <c r="G8">
-        <v>0.604166666666667</v>
+        <v>0.6</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -666,10 +666,10 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>4.14285714285714</v>
+        <v>4.14</v>
       </c>
       <c r="K8">
-        <v>10.5714285714286</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0.166666666666667</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -832,7 +832,7 @@
         <v>168</v>
       </c>
       <c r="G13">
-        <v>0.136904761904762</v>
+        <v>0.14</v>
       </c>
       <c r="H13">
         <v>15</v>
@@ -841,7 +841,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>3.66666666666667</v>
+        <v>3.67</v>
       </c>
       <c r="K13">
         <v>9.5</v>
@@ -876,7 +876,7 @@
         <v>1</v>
       </c>
       <c r="J14">
-        <v>3.33333333333333</v>
+        <v>3.33</v>
       </c>
       <c r="K14">
         <v>11</v>
@@ -1007,7 +1007,7 @@
         <v>47</v>
       </c>
       <c r="G18">
-        <v>0.595744680851064</v>
+        <v>0.6</v>
       </c>
       <c r="H18">
         <v>4</v>
@@ -1156,10 +1156,10 @@
         <v>2</v>
       </c>
       <c r="J22">
-        <v>0.666666666666667</v>
+        <v>0.67</v>
       </c>
       <c r="K22">
-        <v>5.33333333333333</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1182,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="G23">
-        <v>0.772727272727273</v>
+        <v>0.77</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -1287,7 +1287,7 @@
         <v>19</v>
       </c>
       <c r="G26">
-        <v>0.473684210526316</v>
+        <v>0.47</v>
       </c>
       <c r="H26">
         <v>2</v>
@@ -1357,7 +1357,7 @@
         <v>101</v>
       </c>
       <c r="G28">
-        <v>0.415841584158416</v>
+        <v>0.42</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -1366,10 +1366,10 @@
         <v>2</v>
       </c>
       <c r="J28">
-        <v>6.57142857142857</v>
+        <v>6.57</v>
       </c>
       <c r="K28">
-        <v>18.1428571428571</v>
+        <v>18.14</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1427,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="G30">
-        <v>0.666666666666667</v>
+        <v>0.67</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1532,7 +1532,7 @@
         <v>39</v>
       </c>
       <c r="G33">
-        <v>0.41025641025641</v>
+        <v>0.41</v>
       </c>
       <c r="H33">
         <v>4</v>
@@ -1602,7 +1602,7 @@
         <v>37</v>
       </c>
       <c r="G35">
-        <v>0.783783783783784</v>
+        <v>0.78</v>
       </c>
       <c r="H35">
         <v>3</v>
@@ -1611,10 +1611,10 @@
         <v>2</v>
       </c>
       <c r="J35">
-        <v>9.33333333333333</v>
+        <v>9.33</v>
       </c>
       <c r="K35">
-        <v>21.6666666666667</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -1742,7 +1742,7 @@
         <v>14</v>
       </c>
       <c r="G39">
-        <v>0.571428571428571</v>
+        <v>0.57</v>
       </c>
       <c r="H39">
         <v>2</v>
@@ -1777,7 +1777,7 @@
         <v>21</v>
       </c>
       <c r="G40">
-        <v>0.476190476190476</v>
+        <v>0.48</v>
       </c>
       <c r="H40">
         <v>2</v>
@@ -1987,7 +1987,7 @@
         <v>14</v>
       </c>
       <c r="G46">
-        <v>0.857142857142857</v>
+        <v>0.86</v>
       </c>
       <c r="H46">
         <v>4</v>
@@ -2022,7 +2022,7 @@
         <v>113</v>
       </c>
       <c r="G47">
-        <v>0.15929203539823</v>
+        <v>0.16</v>
       </c>
       <c r="H47">
         <v>8</v>
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="J47">
-        <v>2.125</v>
+        <v>2.12</v>
       </c>
       <c r="K47">
         <v>7</v>
@@ -2244,7 +2244,7 @@
         <v>90</v>
       </c>
       <c r="K53">
-        <v>10.8333333333333</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2311,7 +2311,7 @@
         <v>6</v>
       </c>
       <c r="J55">
-        <v>0.666666666666667</v>
+        <v>0.67</v>
       </c>
       <c r="K55">
         <v>9</v>
@@ -2372,7 +2372,7 @@
         <v>34</v>
       </c>
       <c r="G57">
-        <v>0.235294117647059</v>
+        <v>0.24</v>
       </c>
       <c r="H57">
         <v>6</v>
@@ -2384,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="K57">
-        <v>4.66666666666667</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2407,7 +2407,7 @@
         <v>3</v>
       </c>
       <c r="G58">
-        <v>0.666666666666667</v>
+        <v>0.67</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2512,7 +2512,7 @@
         <v>52</v>
       </c>
       <c r="G61">
-        <v>0.365384615384615</v>
+        <v>0.37</v>
       </c>
       <c r="H61">
         <v>9</v>
@@ -2652,7 +2652,7 @@
         <v>12</v>
       </c>
       <c r="G65">
-        <v>0.583333333333333</v>
+        <v>0.58</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -3107,7 +3107,7 @@
         <v>47</v>
       </c>
       <c r="G78">
-        <v>0.659574468085106</v>
+        <v>0.66</v>
       </c>
       <c r="H78">
         <v>7</v>
@@ -3116,10 +3116,10 @@
         <v>2</v>
       </c>
       <c r="J78">
-        <v>4.42857142857143</v>
+        <v>4.43</v>
       </c>
       <c r="K78">
-        <v>11.7142857142857</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3142,7 +3142,7 @@
         <v>3</v>
       </c>
       <c r="G79">
-        <v>0.333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -3212,7 +3212,7 @@
         <v>32</v>
       </c>
       <c r="G81">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="H81">
         <v>3</v>
@@ -3221,7 +3221,7 @@
         <v>7</v>
       </c>
       <c r="J81">
-        <v>3.66666666666667</v>
+        <v>3.67</v>
       </c>
       <c r="K81">
         <v>11</v>
@@ -3247,7 +3247,7 @@
         <v>11</v>
       </c>
       <c r="G82">
-        <v>0.818181818181818</v>
+        <v>0.82</v>
       </c>
       <c r="H82">
         <v>3</v>
@@ -3256,10 +3256,10 @@
         <v>1</v>
       </c>
       <c r="J82">
-        <v>2.33333333333333</v>
+        <v>2.33</v>
       </c>
       <c r="K82">
-        <v>9.66666666666667</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3562,7 +3562,7 @@
         <v>66</v>
       </c>
       <c r="G91">
-        <v>0.0909090909090909</v>
+        <v>0.09</v>
       </c>
       <c r="H91">
         <v>9</v>
@@ -3571,10 +3571,10 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>0.444444444444444</v>
+        <v>0.44</v>
       </c>
       <c r="K91">
-        <v>2.77777777777778</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3597,7 +3597,7 @@
         <v>12</v>
       </c>
       <c r="G92">
-        <v>0.583333333333333</v>
+        <v>0.58</v>
       </c>
       <c r="H92">
         <v>2</v>
@@ -3714,7 +3714,7 @@
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0.666666666666667</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -3772,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="G97">
-        <v>0.333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="H97">
         <v>2</v>
